--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.9893617021276596</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="C2">
-        <v>0.7253521126760564</v>
+        <v>0.795774647887324</v>
       </c>
       <c r="D2">
-        <v>0.2954545454545455</v>
+        <v>0.2416666666666667</v>
       </c>
       <c r="E2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
